--- a/AAII_Financials/Yearly/CCL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CCL_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
   <si>
     <t>CCL</t>
   </si>
@@ -656,197 +656,209 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E7" s="2">
         <v>44895</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44530</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44165</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43799</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43434</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43069</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42704</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42338</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>41973</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41608</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41243</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40877</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>21593000</v>
+      </c>
+      <c r="E8" s="3">
         <v>12168000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1908000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5595000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>20825000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>18881000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>17510000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>16389000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>15714000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>15884000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>15456000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15382000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15793000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>10891000</v>
+      </c>
+      <c r="E9" s="3">
         <v>8359000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2717000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4760000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12908000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>11090000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10501000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>9383000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9447000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10421000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10645000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10320000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10299000</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>10702000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3809000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-809000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>835000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7917000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>7791000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7009000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7006000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6267000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>5463000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4811000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5062000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5494000</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -863,8 +875,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,9 +917,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,93 +962,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E14" s="3">
         <v>441000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1487000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4063000</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>89000</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>13000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>173000</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2370000</v>
+      </c>
+      <c r="E15" s="3">
         <v>2275000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2233000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2241000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2160000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2017000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1846000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1738000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1626000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1637000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1590000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1527000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1522000</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1046,92 +1071,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>19748000</v>
+      </c>
+      <c r="E17" s="3">
         <v>16548000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9667000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14460000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>17549000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>15556000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>14701000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>13318000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13140000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14112000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>14127000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>13740000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>13538000</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1845000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4380000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-7759000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-8865000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3276000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3325000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2809000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3071000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2574000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1772000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1329000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1642000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2255000</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1148,218 +1180,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>159000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-91000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-162000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-493000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>13000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>76000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>55000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-20000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-558000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-259000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>39000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>22000</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4374000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2196000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-5688000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-7117000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5449000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5418000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4710000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4789000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3642000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3150000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2958000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3165000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3799000</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2066000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1609000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1601000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>895000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>229000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>194000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>198000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>223000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>217000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>288000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>319000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>336000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>365000</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-62000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6080000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-9522000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10253000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3060000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3207000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2666000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2828000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1799000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1225000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1049000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1302000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1912000</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E24" s="3">
         <v>14000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-21000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-17000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>71000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>54000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>60000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>49000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>42000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>9000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-6000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4000</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1399,93 +1447,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-75000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6094000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9501000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10236000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2989000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3153000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2606000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2779000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1757000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1216000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1055000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1298000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1912000</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-74000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6093000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9501000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10236000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2990000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3152000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2606000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2779000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1757000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1216000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1055000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1298000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1912000</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1525,9 +1582,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1567,9 +1627,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1609,9 +1672,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1651,93 +1717,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-159000</v>
+      </c>
+      <c r="E32" s="3">
         <v>91000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>162000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>493000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-13000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-76000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-55000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>20000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>558000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>259000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-39000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-22000</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-74000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6093000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9501000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10236000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2990000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3152000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2606000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2779000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1757000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1216000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1055000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1298000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1912000</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1777,98 +1852,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-74000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6093000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9501000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10236000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2990000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3152000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2606000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2779000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1757000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1216000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1055000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1298000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1912000</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E38" s="2">
         <v>44895</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44530</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44165</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43799</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43434</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43069</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42704</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42338</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>41973</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41608</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41243</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40877</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1885,8 +1969,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1903,61 +1988,65 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2415000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4029000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8939000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9513000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>518000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>982000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>395000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>603000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1395000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>331000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>462000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>465000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>450000</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
-        <v>0</v>
+      <c r="D42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>200000</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>8</v>
@@ -1974,8 +2063,8 @@
       <c r="K42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
+      <c r="L42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -1986,177 +2075,192 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>556000</v>
+      </c>
+      <c r="E43" s="3">
         <v>395000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>246000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>427000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>598000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>358000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>312000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>298000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>412000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>486000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>786000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>730000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>293000</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>528000</v>
+      </c>
+      <c r="E44" s="3">
         <v>428000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>356000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>335000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>427000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>450000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>387000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>322000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>330000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>349000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>374000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>390000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>374000</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1767000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2640000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>392000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>288000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>516000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>435000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>502000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>944000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>314000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>322000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>315000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>236000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>195000</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5266000</v>
+      </c>
+      <c r="E46" s="3">
         <v>7492000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10133000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10563000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2059000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2225000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1596000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1689000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2451000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1488000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1937000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1821000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1312000</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2196,93 +2300,102 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>41381000</v>
+      </c>
+      <c r="E48" s="3">
         <v>39961000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>39440000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>39443000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>38131000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>35336000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>34430000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>66449000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>31888000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>65592000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>32905000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>32137000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>32054000</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1748000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1735000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1760000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1993000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4086000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4101000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4167000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4185000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4248000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4397000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4502000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4488000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4652000</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2322,9 +2435,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2364,51 +2480,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>725000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2515000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2011000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1594000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>782000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>739000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>585000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1156000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>650000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>744000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>760000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>715000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>619000</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2448,51 +2570,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>49120000</v>
+      </c>
+      <c r="E54" s="3">
         <v>51703000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>53344000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>53593000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>45058000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>42401000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>40778000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>38881000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>39237000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>39448000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>40104000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>39161000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>38637000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2509,8 +2637,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2527,260 +2656,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1168000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1050000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>797000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>624000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>756000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>730000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>762000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>713000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>627000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>626000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>639000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>549000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>576000</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2089000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2593000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4717000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4826000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1827000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2426000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2202000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1097000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1374000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1725000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1468000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1734000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1300000</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8224000</v>
+      </c>
+      <c r="E59" s="3">
         <v>6962000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4894000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3236000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6544000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6048000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5836000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7002000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4955000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4570000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4613000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5057000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4229000</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11481000</v>
+      </c>
+      <c r="E60" s="3">
         <v>10605000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10408000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8686000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9127000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9204000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8800000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7072000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6956000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6921000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6720000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7340000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6105000</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>28483000</v>
+      </c>
+      <c r="E61" s="3">
         <v>31953000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>28509000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>22130000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9675000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7897000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6993000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8302000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7413000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7363000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8092000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7168000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8053000</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2274000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2080000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2283000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2222000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>891000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>857000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>769000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1820000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1097000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>960000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>736000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>724000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>647000</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2820,9 +2968,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2862,9 +3013,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2904,51 +3058,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>42238000</v>
+      </c>
+      <c r="E66" s="3">
         <v>44638000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>41200000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>33038000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>19693000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>17958000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>16562000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16284000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>15466000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>15244000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>15548000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>15232000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14805000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2965,8 +3125,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3006,9 +3167,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3048,9 +3212,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3090,9 +3257,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3132,51 +3302,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>185000</v>
+      </c>
+      <c r="E72" s="3">
         <v>269000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>6448000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>16075000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>26653000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>25066000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>23292000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>21843000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>20060000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>19158000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>18782000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>18479000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>18349000</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3216,9 +3392,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3258,9 +3437,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3300,51 +3482,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6882000</v>
+      </c>
+      <c r="E76" s="3">
         <v>7065000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12144000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>20555000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>25365000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>24443000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>24216000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22597000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>23771000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>24204000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>24556000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>23929000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>23832000</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3384,98 +3572,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45260</v>
+      </c>
+      <c r="E80" s="2">
         <v>44895</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44530</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44165</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43799</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43434</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43069</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42704</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42338</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>41973</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41608</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41243</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40877</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-74000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6093000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9501000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10236000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2990000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3152000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2606000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2779000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1757000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1216000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1055000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1298000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1912000</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3492,50 +3689,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2370000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2275000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2233000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2241000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2160000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2017000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1846000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1738000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1626000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1637000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1590000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1527000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1522000</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3575,9 +3776,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3617,9 +3821,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3659,9 +3866,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3701,9 +3911,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3743,51 +3956,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4281000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1671000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4108000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-6302000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5476000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5549000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5322000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5134000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4545000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3430000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2834000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2999000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3766000</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3804,50 +4023,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3284000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4940000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3607000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3620000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5429000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3749000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2944000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3062000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2294000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2583000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2149000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2332000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2696000</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3887,9 +4110,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3929,51 +4155,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2810000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4767000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3543000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3240000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5277000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3514000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3122000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3323000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2478000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2507000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2056000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1772000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2646000</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3990,8 +4222,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4002,38 +4235,41 @@
         <v>0</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>-689000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-1387000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-1355000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-1087000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-977000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-816000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-776000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1164000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-779000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-671000</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4073,9 +4309,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4115,9 +4354,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4157,133 +4399,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5089000</v>
+      </c>
+      <c r="E100" s="3">
         <v>3577000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6949000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>18650000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-655000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1460000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2452000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2591000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-942000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1028000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-780000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1190000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1093000</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-79000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-13000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>53000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-9000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>11000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-12000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-61000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-26000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-22000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-6000</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3601000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2940000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-715000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>9161000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-465000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>574000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-241000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-792000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1064000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-131000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>15000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>21000</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/CCL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CCL_YR_FIN.xlsx
@@ -731,13 +731,13 @@
         <v>21593000</v>
       </c>
       <c r="E8" s="3">
-        <v>12168000</v>
+        <v>12169000</v>
       </c>
       <c r="F8" s="3">
         <v>1908000</v>
       </c>
       <c r="G8" s="3">
-        <v>5595000</v>
+        <v>5594000</v>
       </c>
       <c r="H8" s="3">
         <v>20825000</v>
@@ -785,13 +785,13 @@
         <v>4760000</v>
       </c>
       <c r="H9" s="3">
-        <v>12908000</v>
+        <v>9715000</v>
       </c>
       <c r="I9" s="3">
-        <v>11090000</v>
+        <v>8103000</v>
       </c>
       <c r="J9" s="3">
-        <v>10501000</v>
+        <v>10197000</v>
       </c>
       <c r="K9" s="3">
         <v>9383000</v>
@@ -821,22 +821,22 @@
         <v>10702000</v>
       </c>
       <c r="E10" s="3">
-        <v>3809000</v>
+        <v>3810000</v>
       </c>
       <c r="F10" s="3">
         <v>-809000</v>
       </c>
       <c r="G10" s="3">
-        <v>835000</v>
+        <v>834000</v>
       </c>
       <c r="H10" s="3">
-        <v>7917000</v>
+        <v>11110000</v>
       </c>
       <c r="I10" s="3">
-        <v>7791000</v>
+        <v>10778000</v>
       </c>
       <c r="J10" s="3">
-        <v>7009000</v>
+        <v>7313000</v>
       </c>
       <c r="K10" s="3">
         <v>7006000</v>
@@ -972,25 +972,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>111000</v>
+        <v>132000</v>
       </c>
       <c r="E14" s="3">
-        <v>441000</v>
+        <v>471000</v>
       </c>
       <c r="F14" s="3">
-        <v>1487000</v>
+        <v>1504000</v>
       </c>
       <c r="G14" s="3">
-        <v>4063000</v>
+        <v>4415000</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>26000</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="J14" s="3">
-        <v>89000</v>
+        <v>393000</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1078,25 +1078,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>19748000</v>
+        <v>19649000</v>
       </c>
       <c r="E17" s="3">
-        <v>16548000</v>
+        <v>16115000</v>
       </c>
       <c r="F17" s="3">
-        <v>9667000</v>
+        <v>8192000</v>
       </c>
       <c r="G17" s="3">
-        <v>14460000</v>
+        <v>10511000</v>
       </c>
       <c r="H17" s="3">
-        <v>17549000</v>
+        <v>17528000</v>
       </c>
       <c r="I17" s="3">
-        <v>15556000</v>
+        <v>15491000</v>
       </c>
       <c r="J17" s="3">
-        <v>14701000</v>
+        <v>14273000</v>
       </c>
       <c r="K17" s="3">
         <v>13318000</v>
@@ -1123,25 +1123,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1845000</v>
+        <v>1944000</v>
       </c>
       <c r="E18" s="3">
-        <v>-4380000</v>
+        <v>-3946000</v>
       </c>
       <c r="F18" s="3">
-        <v>-7759000</v>
+        <v>-6284000</v>
       </c>
       <c r="G18" s="3">
-        <v>-8865000</v>
+        <v>-4917000</v>
       </c>
       <c r="H18" s="3">
-        <v>3276000</v>
+        <v>3297000</v>
       </c>
       <c r="I18" s="3">
-        <v>3325000</v>
+        <v>3390000</v>
       </c>
       <c r="J18" s="3">
-        <v>2809000</v>
+        <v>3237000</v>
       </c>
       <c r="K18" s="3">
         <v>3071000</v>
@@ -1187,25 +1187,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>159000</v>
+        <v>40000</v>
       </c>
       <c r="E20" s="3">
-        <v>-91000</v>
+        <v>127000</v>
       </c>
       <c r="F20" s="3">
-        <v>-162000</v>
+        <v>145000</v>
       </c>
       <c r="G20" s="3">
-        <v>-493000</v>
+        <v>44000</v>
       </c>
       <c r="H20" s="3">
-        <v>13000</v>
+        <v>27000</v>
       </c>
       <c r="I20" s="3">
-        <v>76000</v>
+        <v>-12000</v>
       </c>
       <c r="J20" s="3">
-        <v>55000</v>
+        <v>-11000</v>
       </c>
       <c r="K20" s="3">
         <v>-20000</v>
@@ -1232,25 +1232,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4374000</v>
+        <v>4274000</v>
       </c>
       <c r="E21" s="3">
-        <v>-2196000</v>
+        <v>-1798000</v>
       </c>
       <c r="F21" s="3">
-        <v>-5688000</v>
+        <v>-4196000</v>
       </c>
       <c r="G21" s="3">
-        <v>-7117000</v>
+        <v>-2720000</v>
       </c>
       <c r="H21" s="3">
-        <v>5449000</v>
+        <v>5430000</v>
       </c>
       <c r="I21" s="3">
-        <v>5418000</v>
+        <v>5419000</v>
       </c>
       <c r="J21" s="3">
-        <v>4710000</v>
+        <v>5094000</v>
       </c>
       <c r="K21" s="3">
         <v>4789000</v>
@@ -1289,7 +1289,7 @@
         <v>895000</v>
       </c>
       <c r="H22" s="3">
-        <v>229000</v>
+        <v>206000</v>
       </c>
       <c r="I22" s="3">
         <v>194000</v>
@@ -1322,10 +1322,10 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-62000</v>
+        <v>-61000</v>
       </c>
       <c r="E23" s="3">
-        <v>-6080000</v>
+        <v>-6079000</v>
       </c>
       <c r="F23" s="3">
         <v>-9522000</v>
@@ -1334,10 +1334,10 @@
         <v>-10253000</v>
       </c>
       <c r="H23" s="3">
-        <v>3060000</v>
+        <v>3061000</v>
       </c>
       <c r="I23" s="3">
-        <v>3207000</v>
+        <v>3206000</v>
       </c>
       <c r="J23" s="3">
         <v>2666000</v>
@@ -1457,10 +1457,10 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-75000</v>
+        <v>-74000</v>
       </c>
       <c r="E26" s="3">
-        <v>-6094000</v>
+        <v>-6093000</v>
       </c>
       <c r="F26" s="3">
         <v>-9501000</v>
@@ -1469,10 +1469,10 @@
         <v>-10236000</v>
       </c>
       <c r="H26" s="3">
-        <v>2989000</v>
+        <v>2990000</v>
       </c>
       <c r="I26" s="3">
-        <v>3153000</v>
+        <v>3152000</v>
       </c>
       <c r="J26" s="3">
         <v>2606000</v>
@@ -1727,25 +1727,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-159000</v>
+        <v>-40000</v>
       </c>
       <c r="E32" s="3">
-        <v>91000</v>
+        <v>-127000</v>
       </c>
       <c r="F32" s="3">
-        <v>162000</v>
+        <v>-145000</v>
       </c>
       <c r="G32" s="3">
-        <v>493000</v>
+        <v>-44000</v>
       </c>
       <c r="H32" s="3">
-        <v>-13000</v>
+        <v>-27000</v>
       </c>
       <c r="I32" s="3">
-        <v>-76000</v>
+        <v>12000</v>
       </c>
       <c r="J32" s="3">
-        <v>-55000</v>
+        <v>11000</v>
       </c>
       <c r="K32" s="3">
         <v>20000</v>
@@ -2039,26 +2039,26 @@
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>8</v>
+      <c r="D42" s="3">
+        <v>1000</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F42" s="3">
         <v>200000</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>8</v>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>8</v>
@@ -2085,16 +2085,16 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>556000</v>
+        <v>850000</v>
       </c>
       <c r="E43" s="3">
-        <v>395000</v>
+        <v>613000</v>
       </c>
       <c r="F43" s="3">
-        <v>246000</v>
+        <v>301000</v>
       </c>
       <c r="G43" s="3">
-        <v>427000</v>
+        <v>273000</v>
       </c>
       <c r="H43" s="3">
         <v>598000</v>
@@ -2174,26 +2174,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>1767000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>2640000</v>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F45" s="3">
-        <v>392000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>288000</v>
+        <v>0</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H45" s="3">
-        <v>516000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>435000</v>
+        <v>31000</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J45" s="3">
-        <v>502000</v>
+        <v>15000</v>
       </c>
       <c r="K45" s="3">
         <v>944000</v>
@@ -2235,7 +2235,7 @@
         <v>2059000</v>
       </c>
       <c r="I46" s="3">
-        <v>2225000</v>
+        <v>2226000</v>
       </c>
       <c r="J46" s="3">
         <v>1596000</v>
@@ -2265,25 +2265,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>139000</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>164000</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>242000</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>289000</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>204000</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>244000</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2490,22 +2490,22 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>725000</v>
+        <v>586000</v>
       </c>
       <c r="E52" s="3">
-        <v>2515000</v>
+        <v>2351000</v>
       </c>
       <c r="F52" s="3">
-        <v>2011000</v>
+        <v>1769000</v>
       </c>
       <c r="G52" s="3">
-        <v>1594000</v>
+        <v>1305000</v>
       </c>
       <c r="H52" s="3">
-        <v>782000</v>
+        <v>397000</v>
       </c>
       <c r="I52" s="3">
-        <v>739000</v>
+        <v>494000</v>
       </c>
       <c r="J52" s="3">
         <v>585000</v>
@@ -2708,25 +2708,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2089000</v>
+        <v>2238000</v>
       </c>
       <c r="E58" s="3">
-        <v>2593000</v>
+        <v>2739000</v>
       </c>
       <c r="F58" s="3">
-        <v>4717000</v>
+        <v>4862000</v>
       </c>
       <c r="G58" s="3">
-        <v>4826000</v>
+        <v>4982000</v>
       </c>
       <c r="H58" s="3">
-        <v>1827000</v>
+        <v>1833000</v>
       </c>
       <c r="I58" s="3">
-        <v>2426000</v>
+        <v>2434000</v>
       </c>
       <c r="J58" s="3">
-        <v>2202000</v>
+        <v>2212000</v>
       </c>
       <c r="K58" s="3">
         <v>1097000</v>
@@ -2753,25 +2753,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>8224000</v>
+        <v>6072000</v>
       </c>
       <c r="E59" s="3">
-        <v>6962000</v>
+        <v>4874000</v>
       </c>
       <c r="F59" s="3">
-        <v>4894000</v>
+        <v>3111000</v>
       </c>
       <c r="G59" s="3">
-        <v>3236000</v>
+        <v>1941000</v>
       </c>
       <c r="H59" s="3">
-        <v>6544000</v>
+        <v>4737000</v>
       </c>
       <c r="I59" s="3">
-        <v>6048000</v>
+        <v>4406000</v>
       </c>
       <c r="J59" s="3">
-        <v>5836000</v>
+        <v>4067000</v>
       </c>
       <c r="K59" s="3">
         <v>7002000</v>
@@ -2813,7 +2813,7 @@
         <v>9127000</v>
       </c>
       <c r="I60" s="3">
-        <v>9204000</v>
+        <v>9205000</v>
       </c>
       <c r="J60" s="3">
         <v>8800000</v>
@@ -2843,25 +2843,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>28483000</v>
+        <v>29669000</v>
       </c>
       <c r="E61" s="3">
-        <v>31953000</v>
+        <v>33142000</v>
       </c>
       <c r="F61" s="3">
-        <v>28509000</v>
+        <v>29750000</v>
       </c>
       <c r="G61" s="3">
-        <v>22130000</v>
+        <v>23408000</v>
       </c>
       <c r="H61" s="3">
-        <v>9675000</v>
+        <v>9684000</v>
       </c>
       <c r="I61" s="3">
-        <v>7897000</v>
+        <v>7908000</v>
       </c>
       <c r="J61" s="3">
-        <v>6993000</v>
+        <v>7010000</v>
       </c>
       <c r="K61" s="3">
         <v>8302000</v>
@@ -2888,25 +2888,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2274000</v>
+        <v>900000</v>
       </c>
       <c r="E62" s="3">
-        <v>2080000</v>
+        <v>703000</v>
       </c>
       <c r="F62" s="3">
-        <v>2283000</v>
+        <v>815000</v>
       </c>
       <c r="G62" s="3">
-        <v>2222000</v>
+        <v>944000</v>
       </c>
       <c r="H62" s="3">
-        <v>891000</v>
+        <v>882000</v>
       </c>
       <c r="I62" s="3">
-        <v>857000</v>
+        <v>845000</v>
       </c>
       <c r="J62" s="3">
-        <v>769000</v>
+        <v>752000</v>
       </c>
       <c r="K62" s="3">
         <v>1820000</v>
@@ -3969,16 +3969,16 @@
         <v>4281000</v>
       </c>
       <c r="E89" s="3">
-        <v>-1671000</v>
+        <v>-1670000</v>
       </c>
       <c r="F89" s="3">
-        <v>-4108000</v>
+        <v>-4109000</v>
       </c>
       <c r="G89" s="3">
-        <v>-6302000</v>
+        <v>-6301000</v>
       </c>
       <c r="H89" s="3">
-        <v>5476000</v>
+        <v>5475000</v>
       </c>
       <c r="I89" s="3">
         <v>5549000</v>
@@ -4238,16 +4238,16 @@
         <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-689000</v>
+        <v>689000</v>
       </c>
       <c r="H96" s="3">
-        <v>-1387000</v>
+        <v>1387000</v>
       </c>
       <c r="I96" s="3">
-        <v>-1355000</v>
+        <v>1355000</v>
       </c>
       <c r="J96" s="3">
-        <v>-1087000</v>
+        <v>1087000</v>
       </c>
       <c r="K96" s="3">
         <v>-977000</v>
@@ -4502,16 +4502,16 @@
         <v>-3601000</v>
       </c>
       <c r="E102" s="3">
-        <v>-2940000</v>
+        <v>-2939000</v>
       </c>
       <c r="F102" s="3">
-        <v>-715000</v>
+        <v>-716000</v>
       </c>
       <c r="G102" s="3">
-        <v>9161000</v>
+        <v>9162000</v>
       </c>
       <c r="H102" s="3">
-        <v>-465000</v>
+        <v>-466000</v>
       </c>
       <c r="I102" s="3">
         <v>574000</v>

--- a/AAII_Financials/Yearly/CCL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CCL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
   <si>
     <t>CCL</t>
   </si>
@@ -656,209 +656,221 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45626</v>
+      </c>
+      <c r="E7" s="2">
         <v>45260</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44895</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44530</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44165</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43799</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43434</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43069</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42704</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42338</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41973</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41608</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41243</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40877</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>25021000</v>
+      </c>
+      <c r="E8" s="3">
         <v>21593000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>12169000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1908000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5594000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>20825000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>18881000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>17510000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>16389000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>15714000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>15884000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15456000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15382000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15793000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>10891000</v>
+        <v>11627000</v>
       </c>
       <c r="E9" s="3">
+        <v>10775000</v>
+      </c>
+      <c r="F9" s="3">
         <v>8359000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2717000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4760000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>9715000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8103000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10197000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9383000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>9447000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10421000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10645000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10320000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10299000</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>10702000</v>
+        <v>13394000</v>
       </c>
       <c r="E10" s="3">
+        <v>10818000</v>
+      </c>
+      <c r="F10" s="3">
         <v>3810000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-809000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>834000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>11110000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>10778000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7313000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7006000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6267000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>5463000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4811000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5062000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5494000</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -876,8 +888,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -920,9 +933,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,99 +981,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>132000</v>
+        <v>38000</v>
       </c>
       <c r="E14" s="3">
-        <v>471000</v>
+        <v>44000</v>
       </c>
       <c r="F14" s="3">
+        <v>464000</v>
+      </c>
+      <c r="G14" s="3">
         <v>1504000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4415000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>26000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>16000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>393000</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>13000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>173000</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2557000</v>
+      </c>
+      <c r="E15" s="3">
         <v>2370000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2275000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2233000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2241000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2160000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2017000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1846000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1738000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1626000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1637000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1590000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1527000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1522000</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1072,98 +1097,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>19649000</v>
+        <v>21502000</v>
       </c>
       <c r="E17" s="3">
-        <v>16115000</v>
+        <v>19737000</v>
       </c>
       <c r="F17" s="3">
+        <v>16122000</v>
+      </c>
+      <c r="G17" s="3">
         <v>8192000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10511000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>17528000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15491000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14273000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13318000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13140000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>14112000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>14127000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>13740000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>13538000</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1944000</v>
+        <v>3519000</v>
       </c>
       <c r="E18" s="3">
-        <v>-3946000</v>
+        <v>1856000</v>
       </c>
       <c r="F18" s="3">
+        <v>-3953000</v>
+      </c>
+      <c r="G18" s="3">
         <v>-6284000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-4917000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3297000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3390000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3237000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3071000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2574000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1772000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1329000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1642000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2255000</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1181,233 +1213,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-96000</v>
+      </c>
+      <c r="E20" s="3">
         <v>40000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>127000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>145000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>44000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>27000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-12000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-11000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-20000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-558000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-259000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>39000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>22000</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>4274000</v>
+        <v>6172000</v>
       </c>
       <c r="E21" s="3">
-        <v>-1798000</v>
+        <v>4186000</v>
       </c>
       <c r="F21" s="3">
+        <v>-1805000</v>
+      </c>
+      <c r="G21" s="3">
         <v>-4196000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2720000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5430000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5419000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5094000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4789000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3642000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3150000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2958000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3165000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3799000</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1755000</v>
+      </c>
+      <c r="E22" s="3">
         <v>2066000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1609000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1601000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>895000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>206000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>194000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>198000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>223000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>217000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>288000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>319000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>336000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>365000</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1915000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-61000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-6079000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9522000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10253000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3061000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3206000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2666000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2828000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1799000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1225000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1049000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1302000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1912000</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E24" s="3">
         <v>13000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>14000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-21000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-17000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>71000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>54000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>60000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>49000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>42000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-6000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4000</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1450,99 +1498,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1916000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-74000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6093000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9501000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10236000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2990000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3152000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2606000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2779000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1757000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1216000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1055000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1298000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1912000</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1916000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-74000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6093000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9501000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10236000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2990000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3152000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2606000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2779000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1757000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1216000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1055000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1298000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1912000</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1585,9 +1642,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1630,9 +1690,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1675,9 +1738,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1720,99 +1786,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-40000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-127000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-145000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-44000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-27000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>12000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>11000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>20000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>558000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>259000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-39000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-22000</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1916000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-74000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6093000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9501000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10236000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2990000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3152000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2606000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2779000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1757000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1216000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1055000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1298000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1912000</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1855,104 +1930,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1916000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-74000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6093000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9501000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10236000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2990000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3152000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2606000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2779000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1757000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1216000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1055000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1298000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1912000</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45626</v>
+      </c>
+      <c r="E38" s="2">
         <v>45260</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44895</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44530</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44165</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43799</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43434</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43069</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42704</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42338</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41973</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41608</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41243</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40877</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1970,8 +2054,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1989,68 +2074,72 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1210000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2415000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4029000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8939000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9513000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>518000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>982000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>395000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>603000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1395000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>331000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>462000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>465000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>450000</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E42" s="3">
         <v>1000</v>
       </c>
       <c r="F42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G42" s="3">
         <v>200000</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -2060,14 +2149,14 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>8</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
+      <c r="M42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -2078,216 +2167,231 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>850000</v>
+        <v>926000</v>
       </c>
       <c r="E43" s="3">
+        <v>556000</v>
+      </c>
+      <c r="F43" s="3">
         <v>613000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>301000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>273000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>598000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>358000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>312000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>298000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>412000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>486000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>786000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>730000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>293000</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>507000</v>
+      </c>
+      <c r="E44" s="3">
         <v>528000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>428000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>356000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>335000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>427000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>450000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>387000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>322000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>330000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>349000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>374000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>390000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>374000</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>1000</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3" t="s">
+      <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H45" s="3">
+      <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3">
         <v>31000</v>
       </c>
-      <c r="I45" s="3" t="s">
+      <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>15000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>944000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>314000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>322000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>315000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>236000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>195000</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3378000</v>
+      </c>
+      <c r="E46" s="3">
         <v>5266000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7492000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10133000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10563000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2059000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2226000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1596000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1689000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2451000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1488000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1937000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1821000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1312000</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>186000</v>
+      </c>
+      <c r="E47" s="3">
         <v>139000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>164000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>242000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>289000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>204000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>244000</v>
       </c>
-      <c r="J47" s="3" t="s">
+      <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -2303,99 +2407,108 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>43163000</v>
+      </c>
+      <c r="E48" s="3">
         <v>41381000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>39961000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>39440000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>39443000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>38131000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>35336000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>34430000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>66449000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>31888000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>65592000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>32905000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>32137000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>32054000</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1742000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1748000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1735000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1760000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1993000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4086000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4101000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4167000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4185000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4248000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4397000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4502000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4488000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4652000</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2438,9 +2551,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2483,54 +2599,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>588000</v>
+      </c>
+      <c r="E52" s="3">
         <v>586000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2351000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1769000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1305000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>397000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>494000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>585000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1156000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>650000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>744000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>760000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>715000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>619000</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2573,54 +2695,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>49057000</v>
+      </c>
+      <c r="E54" s="3">
         <v>49120000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>51703000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>53344000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>53593000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>45058000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>42401000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>40778000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>38881000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>39237000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>39448000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>40104000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>39161000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>38637000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2638,8 +2766,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2657,278 +2786,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1133000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1168000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1050000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>797000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>624000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>756000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>730000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>762000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>713000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>627000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>626000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>639000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>549000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>576000</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1701000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2238000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2739000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4862000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4982000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1833000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2434000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2212000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1097000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1374000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1725000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1468000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1734000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1300000</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6425000</v>
+      </c>
+      <c r="E59" s="3">
         <v>6072000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4874000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3111000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1941000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4737000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4406000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4067000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7002000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4955000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4570000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4613000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5057000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4229000</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11617000</v>
+      </c>
+      <c r="E60" s="3">
         <v>11481000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10605000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10408000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8686000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9127000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9205000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8800000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7072000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6956000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6921000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6720000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7340000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6105000</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>27179000</v>
+      </c>
+      <c r="E61" s="3">
         <v>29669000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>33142000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>29750000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>23408000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9684000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7908000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7010000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8302000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7413000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7363000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8092000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7168000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>8053000</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>800000</v>
+      </c>
+      <c r="E62" s="3">
         <v>900000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>703000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>815000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>944000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>882000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>845000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>752000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1820000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1097000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>960000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>736000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>724000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>647000</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2971,9 +3119,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3016,9 +3167,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3061,54 +3215,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>39806000</v>
+      </c>
+      <c r="E66" s="3">
         <v>42238000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>44638000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>41200000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>33038000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>19693000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>17958000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16562000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16284000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>15466000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>15244000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>15548000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15232000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14805000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3126,8 +3286,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3170,9 +3331,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3215,9 +3379,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3260,9 +3427,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3305,54 +3475,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2101000</v>
+      </c>
+      <c r="E72" s="3">
         <v>185000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>269000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6448000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>16075000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>26653000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>25066000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>23292000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>21843000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>20060000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>19158000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>18782000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>18479000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>18349000</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3395,9 +3571,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3440,9 +3619,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3485,54 +3667,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9251000</v>
+      </c>
+      <c r="E76" s="3">
         <v>6882000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7065000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12144000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20555000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>25365000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>24443000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>24216000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>22597000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>23771000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>24204000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>24556000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>23929000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>23832000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3575,104 +3763,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45626</v>
+      </c>
+      <c r="E80" s="2">
         <v>45260</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44895</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44530</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44165</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43799</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43434</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43069</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42704</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42338</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41973</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41608</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41243</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40877</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1916000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-74000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6093000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9501000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10236000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2990000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3152000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2606000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2779000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1757000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1216000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1055000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1298000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1912000</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3690,53 +3887,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2557000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2370000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2275000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2233000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2241000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2160000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2017000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1846000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1738000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1626000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1637000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1590000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1527000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1522000</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3779,9 +3980,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3824,9 +4028,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3869,9 +4076,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3914,9 +4124,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3959,54 +4172,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5923000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4281000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1670000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4109000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-6301000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5475000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5549000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5322000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5134000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4545000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3430000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2834000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2999000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3766000</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4024,53 +4243,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4626000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3284000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4940000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3607000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3620000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5429000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3749000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2944000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3062000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2294000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2583000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2149000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2332000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2696000</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4113,9 +4336,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4158,54 +4384,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4535000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2810000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4767000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3543000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3240000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5277000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3514000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3122000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3323000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2478000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2507000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2056000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1772000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2646000</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4223,8 +4455,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4238,38 +4471,41 @@
         <v>0</v>
       </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>689000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1387000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1355000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1087000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-977000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-816000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-776000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1164000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-779000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-671000</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4312,9 +4548,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4357,9 +4596,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4402,142 +4644,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2584000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5089000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3577000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6949000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>18650000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-655000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1460000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2452000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2591000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-942000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1028000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-780000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1190000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1093000</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E101" s="3">
         <v>17000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-79000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-13000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>53000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-9000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>11000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-12000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-61000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-26000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-22000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1204000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3601000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2939000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-716000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>9162000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-466000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>574000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-241000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-792000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1064000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-131000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>15000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>21000</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/CCL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CCL_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
   <si>
     <t>CCL</t>
   </si>
@@ -656,221 +656,233 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45991</v>
+      </c>
+      <c r="E7" s="2">
         <v>45626</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45260</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44895</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44530</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44165</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43799</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43434</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43069</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42704</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42338</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41973</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41608</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41243</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40877</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>26622000</v>
+      </c>
+      <c r="E8" s="3">
         <v>25021000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>21593000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>12169000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1908000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5594000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>20825000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>18881000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>17510000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>16389000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>15714000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15884000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15456000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15382000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>15793000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>11834000</v>
+      </c>
+      <c r="E9" s="3">
         <v>11627000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10775000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8359000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2717000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4760000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>9715000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8103000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10197000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>9383000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>9447000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10421000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10645000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10320000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10299000</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>14788000</v>
+      </c>
+      <c r="E10" s="3">
         <v>13394000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>10818000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3810000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-809000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>834000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>11110000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>10778000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7313000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>7006000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6267000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>5463000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4811000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5062000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5494000</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -889,8 +901,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -936,9 +949,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,105 +1000,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>297000</v>
+      </c>
+      <c r="E14" s="3">
         <v>38000</v>
       </c>
-      <c r="E14" s="3">
-        <v>44000</v>
-      </c>
       <c r="F14" s="3">
+        <v>23000</v>
+      </c>
+      <c r="G14" s="3">
         <v>464000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1504000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4415000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>26000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>16000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>393000</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>13000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>173000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2790000</v>
+      </c>
+      <c r="E15" s="3">
         <v>2557000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2370000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2275000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2233000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2241000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2160000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2017000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1846000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1738000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1626000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1637000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1590000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1527000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1522000</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1098,104 +1123,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>22263000</v>
+      </c>
+      <c r="E17" s="3">
         <v>21502000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>19737000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>16122000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8192000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>10511000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>17528000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15491000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>14273000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13318000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>13140000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>14112000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>14127000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>13740000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>13538000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4359000</v>
+      </c>
+      <c r="E18" s="3">
         <v>3519000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1856000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3953000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-6284000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-4917000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3297000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3390000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3237000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3071000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2574000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1772000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1329000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1642000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2255000</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1214,248 +1246,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-96000</v>
       </c>
-      <c r="E20" s="3">
-        <v>40000</v>
-      </c>
       <c r="F20" s="3">
+        <v>61000</v>
+      </c>
+      <c r="G20" s="3">
         <v>127000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>145000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>44000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>27000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-12000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-11000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-20000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-558000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-259000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>39000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>22000</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>7157000</v>
+      </c>
+      <c r="E21" s="3">
         <v>6172000</v>
       </c>
-      <c r="E21" s="3">
-        <v>4186000</v>
-      </c>
       <c r="F21" s="3">
+        <v>4165000</v>
+      </c>
+      <c r="G21" s="3">
         <v>-1805000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-4196000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2720000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5430000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5419000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5094000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4789000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3642000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3150000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2958000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3165000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3799000</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1349000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1755000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2066000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1609000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1601000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>895000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>206000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>194000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>198000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>223000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>217000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>288000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>319000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>336000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>365000</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2772000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1915000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-61000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-6079000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-9522000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-10253000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3061000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3206000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2666000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2828000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1799000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1225000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1049000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1302000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1912000</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>13000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>14000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-21000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-17000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>71000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>54000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>60000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>49000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>42000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>9000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-6000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4000</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1501,105 +1549,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2760000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1916000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-74000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6093000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9501000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-10236000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2990000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3152000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2606000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2779000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1757000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1216000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1055000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1298000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1912000</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2760000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1916000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-74000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6093000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9501000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-10236000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2990000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3152000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2606000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2779000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1757000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1216000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1055000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1298000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1912000</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1645,9 +1702,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1693,9 +1753,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1741,9 +1804,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1789,105 +1855,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E32" s="3">
         <v>96000</v>
       </c>
-      <c r="E32" s="3">
-        <v>-40000</v>
-      </c>
       <c r="F32" s="3">
+        <v>-61000</v>
+      </c>
+      <c r="G32" s="3">
         <v>-127000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-145000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-44000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-27000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>12000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>11000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>20000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>558000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>259000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-39000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-22000</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2760000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1916000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-74000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6093000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9501000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-10236000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2990000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3152000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2606000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2779000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1757000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1216000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1055000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1298000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1912000</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1933,110 +2008,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2760000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1916000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-74000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6093000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9501000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-10236000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2990000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3152000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2606000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2779000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1757000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1216000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1055000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1298000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1912000</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45991</v>
+      </c>
+      <c r="E38" s="2">
         <v>45626</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45260</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44895</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44530</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44165</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43799</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43434</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43069</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42704</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42338</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41973</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41608</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41243</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40877</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2055,8 +2139,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2075,74 +2160,78 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1928000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1210000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2415000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4029000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8939000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9513000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>518000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>982000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>395000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>603000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1395000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>331000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>462000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>465000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>450000</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <v>1000</v>
       </c>
       <c r="G42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H42" s="3">
         <v>200000</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -2152,14 +2241,14 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>8</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -2170,231 +2259,246 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1041000</v>
+      </c>
+      <c r="E43" s="3">
         <v>926000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>556000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>613000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>301000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>273000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>598000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>358000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>312000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>298000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>412000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>486000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>786000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>730000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>293000</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>505000</v>
+      </c>
+      <c r="E44" s="3">
         <v>507000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>528000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>428000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>356000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>335000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>427000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>450000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>387000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>322000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>330000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>349000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>374000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>390000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>374000</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>1000</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3" t="s">
+      <c r="G45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I45" s="3">
+      <c r="H45" s="3">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3">
         <v>31000</v>
       </c>
-      <c r="J45" s="3" t="s">
+      <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>15000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>944000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>314000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>322000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>315000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>236000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>195000</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4219000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3378000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5266000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7492000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10133000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10563000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2059000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2226000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1596000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1689000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2451000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1488000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1937000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1821000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1312000</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>186000</v>
+        <v>221000</v>
       </c>
       <c r="E47" s="3">
+        <v>184000</v>
+      </c>
+      <c r="F47" s="3">
         <v>139000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>164000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>242000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>289000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>204000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>244000</v>
       </c>
-      <c r="K47" s="3" t="s">
+      <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -2410,105 +2514,114 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>44822000</v>
+      </c>
+      <c r="E48" s="3">
         <v>43163000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>41381000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>39961000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>39440000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>39443000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>38131000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>35336000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>34430000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>66449000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>31888000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>65592000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>32905000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>32137000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>32054000</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1756000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1742000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1748000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1735000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1760000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1993000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4086000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4101000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4167000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4185000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4248000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4397000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4502000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4488000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4652000</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2554,9 +2667,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2602,57 +2718,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>588000</v>
+        <v>669000</v>
       </c>
       <c r="E52" s="3">
+        <v>590000</v>
+      </c>
+      <c r="F52" s="3">
         <v>586000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2351000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1769000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1305000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>397000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>494000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>585000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1156000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>650000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>744000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>760000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>715000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>619000</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2698,57 +2820,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>51687000</v>
+      </c>
+      <c r="E54" s="3">
         <v>49057000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>49120000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>51703000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>53344000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>53593000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>45058000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>42401000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>40778000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>38881000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>39237000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>39448000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>40104000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>39161000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>38637000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2767,8 +2895,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2787,296 +2916,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1245000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1133000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1168000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1050000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>797000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>624000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>756000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>730000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>762000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>713000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>627000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>626000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>639000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>549000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>576000</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2778000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1701000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2238000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2739000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4862000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4982000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1833000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2434000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2212000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1097000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1374000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1725000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1468000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1734000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1300000</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6830000</v>
+      </c>
+      <c r="E59" s="3">
         <v>6425000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6072000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4874000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3111000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1941000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4737000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4406000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4067000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7002000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4955000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4570000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4613000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5057000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4229000</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13092000</v>
+      </c>
+      <c r="E60" s="3">
         <v>11617000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11481000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10605000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10408000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8686000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9127000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9205000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8800000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7072000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6956000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6921000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6720000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7340000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6105000</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>27179000</v>
+        <v>25215000</v>
       </c>
       <c r="E61" s="3">
+        <v>27175000</v>
+      </c>
+      <c r="F61" s="3">
         <v>29669000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>33142000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>29750000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>23408000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9684000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7908000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7010000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8302000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7413000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7363000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8092000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7168000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8053000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>800000</v>
+        <v>875000</v>
       </c>
       <c r="E62" s="3">
+        <v>804000</v>
+      </c>
+      <c r="F62" s="3">
         <v>900000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>703000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>815000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>944000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>882000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>845000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>752000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1820000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1097000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>960000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>736000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>724000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>647000</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3122,9 +3270,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3170,9 +3321,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3218,57 +3372,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>39403000</v>
+      </c>
+      <c r="E66" s="3">
         <v>39806000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>42238000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>44638000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>41200000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>33038000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>19693000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>17958000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16562000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16284000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>15466000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>15244000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15548000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>15232000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>14805000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3287,8 +3447,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3334,9 +3495,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3382,9 +3546,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3430,9 +3597,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3478,57 +3648,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4817000</v>
+      </c>
+      <c r="E72" s="3">
         <v>2101000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>185000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>269000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>6448000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>16075000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>26653000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>25066000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>23292000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>21843000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>20060000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>19158000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>18782000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>18479000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>18349000</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3574,9 +3750,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3622,9 +3801,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3670,57 +3852,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12284000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9251000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6882000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7065000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12144000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20555000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>25365000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>24443000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>24216000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>22597000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>23771000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>24204000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>24556000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>23929000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>23832000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3766,110 +3954,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45991</v>
+      </c>
+      <c r="E80" s="2">
         <v>45626</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45260</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44895</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44530</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44165</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43799</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43434</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43069</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42704</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42338</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41973</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41608</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41243</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40877</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2760000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1916000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-74000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6093000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9501000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-10236000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2990000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3152000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2606000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2779000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1757000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1216000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1055000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1298000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1912000</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3888,56 +4085,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2790000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2557000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2370000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2275000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2233000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2241000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2160000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2017000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1846000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1738000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1626000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1637000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1590000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1527000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1522000</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3983,9 +4184,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4031,9 +4235,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4079,9 +4286,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4127,9 +4337,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4175,57 +4388,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6218000</v>
+      </c>
+      <c r="E89" s="3">
         <v>5923000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4281000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1670000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4109000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6301000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5475000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5549000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5322000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5134000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4545000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3430000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2834000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2999000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3766000</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4244,56 +4463,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3611000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4626000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3284000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4940000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3607000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3620000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5429000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3749000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2944000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3062000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2294000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2583000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2149000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2332000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2696000</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4339,9 +4562,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4387,57 +4613,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3321000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4535000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2810000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4767000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3543000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3240000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5277000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3514000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3122000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3323000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2478000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2507000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2056000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1772000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2646000</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4456,8 +4688,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4474,38 +4707,41 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>689000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1387000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1355000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>1087000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-977000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-816000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-776000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1164000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-779000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-671000</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4551,9 +4787,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4599,9 +4838,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4647,151 +4889,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2189000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2584000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5089000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3577000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>6949000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>18650000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-655000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1460000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2452000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2591000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-942000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1028000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-780000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1190000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1093000</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-8000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>17000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-79000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-13000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>53000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-9000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>11000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-12000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-61000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-26000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-22000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-6000</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>727000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1204000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3601000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2939000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-716000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>9162000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-466000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>574000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-241000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-792000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1064000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-131000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>15000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>21000</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
